--- a/Timetable.xlsx
+++ b/Timetable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9324" tabRatio="500"/>
+    <workbookView windowWidth="22188" windowHeight="8724" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Aytumn_2026" sheetId="8" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="195">
   <si>
     <t>Сентябрь</t>
   </si>
@@ -102,7 +102,7 @@
     <t>22 окт</t>
   </si>
   <si>
-    <t>1-пара</t>
+    <t>2-пара</t>
   </si>
   <si>
     <t>Линейная алгебра</t>
@@ -147,9 +147,6 @@
     <t>12 ноя</t>
   </si>
   <si>
-    <t>2-пара</t>
-  </si>
-  <si>
     <t>GLM для нормально распределенных данных</t>
   </si>
   <si>
@@ -177,28 +174,49 @@
     <t>26 ноя</t>
   </si>
   <si>
+    <t>30 ноя</t>
+  </si>
+  <si>
     <t>GLMM для нормально-распределенных данных</t>
   </si>
   <si>
-    <t>30 ноя</t>
+    <t>3 дек</t>
+  </si>
+  <si>
+    <t>7 дек</t>
   </si>
   <si>
     <t>Моделирование структуры дисперсии в смешаных моделях</t>
   </si>
   <si>
-    <t>7 дек</t>
+    <t>четв</t>
+  </si>
+  <si>
+    <t>10 дек</t>
+  </si>
+  <si>
+    <t>Декабрь</t>
+  </si>
+  <si>
+    <t>14 дек</t>
   </si>
   <si>
     <t>GLMM для счетных данных</t>
   </si>
   <si>
-    <t>15 дек</t>
+    <t>17 дек</t>
+  </si>
+  <si>
+    <t>21 дек</t>
   </si>
   <si>
     <t>GAM + на самостоятельное GLMM для бинарных данных</t>
   </si>
   <si>
-    <t>Декабрь</t>
+    <t>28 дек</t>
+  </si>
+  <si>
+    <t>Зачет в 3058</t>
   </si>
   <si>
     <t>11 сент</t>
@@ -844,7 +862,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="57">
+  <fills count="55">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1081,12 +1099,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1160,12 +1172,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1399,59 +1405,59 @@
     <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1656,12 +1662,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2330,13 +2332,13 @@
       <c r="I9" t="s">
         <v>20</v>
       </c>
-      <c r="J9" s="82" t="s">
+      <c r="J9" s="80" t="s">
         <v>27</v>
       </c>
       <c r="K9" t="s">
         <v>22</v>
       </c>
-      <c r="L9" s="83" t="s">
+      <c r="L9" s="82" t="s">
         <v>28</v>
       </c>
       <c r="M9" s="2" t="s">
@@ -2371,7 +2373,7 @@
       <c r="I10" t="s">
         <v>3</v>
       </c>
-      <c r="J10" s="82" t="s">
+      <c r="J10" s="80" t="s">
         <v>30</v>
       </c>
       <c r="K10" t="s">
@@ -2412,13 +2414,13 @@
       <c r="I11" t="s">
         <v>20</v>
       </c>
-      <c r="J11" s="82" t="s">
+      <c r="J11" s="80" t="s">
         <v>32</v>
       </c>
       <c r="K11" t="s">
         <v>22</v>
       </c>
-      <c r="L11" s="83" t="s">
+      <c r="L11" s="82" t="s">
         <v>28</v>
       </c>
       <c r="M11" s="2" t="s">
@@ -2459,7 +2461,7 @@
       <c r="K12" t="s">
         <v>12</v>
       </c>
-      <c r="L12" s="83" t="s">
+      <c r="L12" s="82" t="s">
         <v>28</v>
       </c>
       <c r="M12" s="2" t="s">
@@ -2496,13 +2498,13 @@
         <v>36</v>
       </c>
       <c r="K13" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="L13" s="59" t="s">
         <v>16</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2520,7 +2522,7 @@
         <v>3</v>
       </c>
       <c r="J14" s="80" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K14" t="s">
         <v>12</v>
@@ -2529,14 +2531,14 @@
         <v>13</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="75" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="75"/>
       <c r="C15" s="75"/>
@@ -2549,13 +2551,13 @@
         <v>20</v>
       </c>
       <c r="J15" s="81" t="s">
+        <v>41</v>
+      </c>
+      <c r="K15" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="83" t="s">
         <v>42</v>
-      </c>
-      <c r="K15" t="s">
-        <v>37</v>
-      </c>
-      <c r="M15" s="84" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -2572,8 +2574,8 @@
       <c r="I16" t="s">
         <v>3</v>
       </c>
-      <c r="J16" s="85" t="s">
-        <v>44</v>
+      <c r="J16" s="81" t="s">
+        <v>43</v>
       </c>
       <c r="K16" t="s">
         <v>12</v>
@@ -2582,7 +2584,7 @@
         <v>13</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2611,22 +2613,17 @@
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="J17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L17" t="s">
-        <v>13</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="M17" s="83" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="77">
@@ -2655,16 +2652,16 @@
         <v>3</v>
       </c>
       <c r="J18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K18" t="s">
         <v>12</v>
       </c>
-      <c r="L18" s="83" t="s">
-        <v>28</v>
+      <c r="L18" t="s">
+        <v>13</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2693,22 +2690,17 @@
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="J19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K19" t="s">
-        <v>12</v>
-      </c>
-      <c r="L19" t="s">
-        <v>13</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="M19" s="83" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="77">
@@ -2737,16 +2729,16 @@
         <v>3</v>
       </c>
       <c r="J20" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K20" t="s">
         <v>12</v>
       </c>
-      <c r="L20" t="s">
-        <v>13</v>
+      <c r="L20" s="82" t="s">
+        <v>28</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2762,12 +2754,22 @@
       <c r="F21" s="73"/>
       <c r="G21" s="73"/>
       <c r="H21" s="1"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+      <c r="I21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J21" t="s">
+        <v>52</v>
+      </c>
+      <c r="K21" t="s">
+        <v>22</v>
+      </c>
+      <c r="M21" s="83" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="75" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B22" s="75"/>
       <c r="C22" s="75"/>
@@ -2776,6 +2778,21 @@
       <c r="F22" s="75"/>
       <c r="G22" s="75"/>
       <c r="H22" s="1"/>
+      <c r="I22" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" t="s">
+        <v>54</v>
+      </c>
+      <c r="K22" t="s">
+        <v>12</v>
+      </c>
+      <c r="L22" t="s">
+        <v>13</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
     </row>
@@ -2800,10 +2817,19 @@
         <v>6</v>
       </c>
       <c r="H23" s="1"/>
-      <c r="I23"/>
-      <c r="J23"/>
-      <c r="K23"/>
-      <c r="L23" s="2"/>
+      <c r="I23" t="s">
+        <v>51</v>
+      </c>
+      <c r="J23" t="s">
+        <v>56</v>
+      </c>
+      <c r="K23" t="s">
+        <v>22</v>
+      </c>
+      <c r="M23" s="83" t="s">
+        <v>42</v>
+      </c>
+      <c r="O23" s="2"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24">
@@ -2828,6 +2854,22 @@
         <v>13</v>
       </c>
       <c r="H24" s="1"/>
+      <c r="I24" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" t="s">
+        <v>57</v>
+      </c>
+      <c r="K24" t="s">
+        <v>12</v>
+      </c>
+      <c r="L24" t="s">
+        <v>13</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="N24" s="2"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25">
@@ -2852,6 +2894,15 @@
         <v>21</v>
       </c>
       <c r="H25" s="1"/>
+      <c r="J25" t="s">
+        <v>59</v>
+      </c>
+      <c r="K25" t="s">
+        <v>22</v>
+      </c>
+      <c r="L25" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="26" spans="1:15">
       <c r="A26">
@@ -2979,16 +3030,16 @@
         <v>6</v>
       </c>
       <c r="J3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="N3" t="s">
         <v>3</v>
       </c>
       <c r="O3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="P3" s="58" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q3" t="s">
         <v>2</v>
@@ -3021,10 +3072,10 @@
         <v>3</v>
       </c>
       <c r="J4" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="K4" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L4" t="s">
         <v>2</v>
@@ -3058,10 +3109,10 @@
         <v>6</v>
       </c>
       <c r="J5" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K5" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L5" t="s">
         <v>10</v>
@@ -3070,13 +3121,13 @@
         <v>3</v>
       </c>
       <c r="O5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="P5" s="60" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -3106,10 +3157,10 @@
         <v>3</v>
       </c>
       <c r="J6" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="K6" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L6" t="s">
         <v>14</v>
@@ -3118,13 +3169,13 @@
         <v>6</v>
       </c>
       <c r="O6" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="P6" s="63" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="Q6" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -3146,10 +3197,10 @@
         <v>6</v>
       </c>
       <c r="J7" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K7" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L7" t="s">
         <v>17</v>
@@ -3158,13 +3209,13 @@
         <v>3</v>
       </c>
       <c r="O7" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P7" s="64" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -3182,10 +3233,10 @@
         <v>3</v>
       </c>
       <c r="J8" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="K8" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L8" t="s">
         <v>19</v>
@@ -3197,10 +3248,10 @@
         <v>11</v>
       </c>
       <c r="P8" s="65" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -3224,10 +3275,10 @@
         <v>6</v>
       </c>
       <c r="J9" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L9" t="s">
         <v>23</v>
@@ -3236,13 +3287,13 @@
         <v>3</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P9" s="66" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -3272,7 +3323,7 @@
         <v>3</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>6</v>
@@ -3281,7 +3332,7 @@
         <v>15</v>
       </c>
       <c r="P10" s="68" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>26</v>
@@ -3314,16 +3365,16 @@
         <v>6</v>
       </c>
       <c r="J11" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="P11" s="66" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>29</v>
@@ -3356,10 +3407,10 @@
         <v>3</v>
       </c>
       <c r="J12" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="K12" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>26</v>
@@ -3371,7 +3422,7 @@
         <v>18</v>
       </c>
       <c r="P12" s="66" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>31</v>
@@ -3402,10 +3453,10 @@
         <v>6</v>
       </c>
       <c r="J13" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="K13" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>29</v>
@@ -3414,10 +3465,10 @@
         <v>3</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="P13" s="68" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>33</v>
@@ -3436,10 +3487,10 @@
         <v>3</v>
       </c>
       <c r="J14" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K14" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>31</v>
@@ -3451,7 +3502,7 @@
         <v>25</v>
       </c>
       <c r="P14" s="68" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>35</v>
@@ -3459,7 +3510,7 @@
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="75" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="75"/>
       <c r="C15" s="75"/>
@@ -3472,10 +3523,10 @@
         <v>6</v>
       </c>
       <c r="J15" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="K15" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>33</v>
@@ -3496,10 +3547,10 @@
         <v>3</v>
       </c>
       <c r="J16" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K16" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>35</v>
@@ -3508,13 +3559,13 @@
         <v>3</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="P16" s="64" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -3544,13 +3595,13 @@
         <v>6</v>
       </c>
       <c r="J17" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K17" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>6</v>
@@ -3559,10 +3610,10 @@
         <v>34</v>
       </c>
       <c r="P17" s="64" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -3592,25 +3643,25 @@
         <v>3</v>
       </c>
       <c r="J18" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="K18" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="P18" s="66" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -3640,22 +3691,22 @@
         <v>6</v>
       </c>
       <c r="J19" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="K19" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P19" s="68" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="Q19" s="2" t="s">
         <v>47</v>
@@ -3688,10 +3739,10 @@
         <v>3</v>
       </c>
       <c r="J20" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K20" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>47</v>
@@ -3700,13 +3751,13 @@
         <v>3</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="P20" s="66" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -3724,30 +3775,30 @@
         <v>6</v>
       </c>
       <c r="J21" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="K21" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P21" s="68" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="75" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B22" s="75"/>
       <c r="C22" s="75"/>
@@ -3760,25 +3811,25 @@
         <v>3</v>
       </c>
       <c r="J22" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="K22" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="P22" s="66" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -3806,13 +3857,13 @@
         <v>6</v>
       </c>
       <c r="J23" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="K23" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -3981,10 +4032,10 @@
         <v>3</v>
       </c>
       <c r="J3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K3" s="58" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L3" t="s">
         <v>2</v>
@@ -4017,13 +4068,13 @@
         <v>6</v>
       </c>
       <c r="J4" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="K4" s="59" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -4053,13 +4104,13 @@
         <v>3</v>
       </c>
       <c r="J5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K5" s="60" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -4089,13 +4140,13 @@
         <v>6</v>
       </c>
       <c r="J6" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K6" s="63" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L6" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -4112,13 +4163,13 @@
         <v>3</v>
       </c>
       <c r="J7" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K7" s="64" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -4139,10 +4190,10 @@
         <v>11</v>
       </c>
       <c r="K8" s="65" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -4167,13 +4218,13 @@
         <v>3</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="K9" s="66" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -4206,7 +4257,7 @@
         <v>15</v>
       </c>
       <c r="K10" s="68" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>26</v>
@@ -4239,10 +4290,10 @@
         <v>3</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="K11" s="66" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>29</v>
@@ -4278,7 +4329,7 @@
         <v>18</v>
       </c>
       <c r="K12" s="66" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>31</v>
@@ -4306,10 +4357,10 @@
         <v>3</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="K13" s="68" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>33</v>
@@ -4330,7 +4381,7 @@
         <v>25</v>
       </c>
       <c r="K14" s="68" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>35</v>
@@ -4338,7 +4389,7 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -4364,13 +4415,13 @@
         <v>3</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="K16" s="64" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -4403,10 +4454,10 @@
         <v>34</v>
       </c>
       <c r="K17" s="64" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -4436,13 +4487,13 @@
         <v>3</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="K18" s="66" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -4472,10 +4523,10 @@
         <v>6</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K19" s="68" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>47</v>
@@ -4508,18 +4559,18 @@
         <v>3</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="K20" s="66" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -4532,13 +4583,13 @@
         <v>6</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K21" s="68" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -4568,13 +4619,13 @@
         <v>3</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="K22" s="66" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -4774,10 +4825,10 @@
         <v>6</v>
       </c>
       <c r="J4" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="K4" s="51" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="L4" t="s">
         <v>2</v>
@@ -4810,13 +4861,13 @@
         <v>3</v>
       </c>
       <c r="J5" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="K5" s="52" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -4846,13 +4897,13 @@
         <v>6</v>
       </c>
       <c r="J6" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="K6" s="51" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="L6" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -4877,13 +4928,13 @@
         <v>3</v>
       </c>
       <c r="J7" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="K7" s="54" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -4901,13 +4952,13 @@
         <v>6</v>
       </c>
       <c r="J8" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="K8" s="55" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -4926,13 +4977,13 @@
         <v>3</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="K9" s="55" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -4962,10 +5013,10 @@
         <v>6</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="K10" s="54" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>26</v>
@@ -4998,10 +5049,10 @@
         <v>3</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K11" s="55" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>29</v>
@@ -5034,10 +5085,10 @@
         <v>6</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K12" s="55" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>31</v>
@@ -5070,10 +5121,10 @@
         <v>3</v>
       </c>
       <c r="J13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="K13" s="54" t="s">
         <v>97</v>
-      </c>
-      <c r="K13" s="54" t="s">
-        <v>91</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>33</v>
@@ -5094,10 +5145,10 @@
         <v>6</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K14" s="54" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>35</v>
@@ -5105,7 +5156,7 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -5139,13 +5190,13 @@
         <v>3</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="K16" s="54" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -5175,13 +5226,13 @@
         <v>6</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K17" s="54" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -5211,13 +5262,13 @@
         <v>3</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="K18" s="55" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -5247,10 +5298,10 @@
         <v>6</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="K19" s="54" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>47</v>
@@ -5275,18 +5326,18 @@
         <v>3</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="K20" s="55" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -5299,13 +5350,13 @@
         <v>6</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="K21" s="54" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -5328,13 +5379,13 @@
         <v>3</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="K22" s="55" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -5557,13 +5608,13 @@
         <v>6</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="M4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -5590,16 +5641,16 @@
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="39" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="J5" s="39"/>
       <c r="K5" s="39"/>
       <c r="L5" s="2"/>
       <c r="M5" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -5626,12 +5677,12 @@
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="40" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="J6" s="40"/>
       <c r="K6" s="40"/>
       <c r="N6" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -5655,13 +5706,13 @@
         <v>3</v>
       </c>
       <c r="J7" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="K7" s="41" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="M7" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -5679,13 +5730,13 @@
         <v>6</v>
       </c>
       <c r="J8" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="K8" s="42" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -5706,14 +5757,14 @@
         <v>3</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -5743,14 +5794,14 @@
         <v>6</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -5780,10 +5831,10 @@
         <v>3</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="K11" s="46" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2" t="s">
@@ -5817,10 +5868,10 @@
         <v>6</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2" t="s">
@@ -5854,10 +5905,10 @@
         <v>3</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2" t="s">
@@ -5866,7 +5917,7 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -5879,10 +5930,10 @@
         <v>6</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="K14" s="46" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2" t="s">
@@ -5916,10 +5967,10 @@
         <v>3</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="K15" s="46" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2" t="s">
@@ -5953,11 +6004,11 @@
         <v>6</v>
       </c>
       <c r="J16" s="50" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -5987,14 +6038,14 @@
         <v>3</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="K17" s="46" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -6024,14 +6075,14 @@
         <v>6</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="K18" s="46" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -6051,19 +6102,19 @@
         <v>3</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -6076,10 +6127,10 @@
         <v>6</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="K20" s="46" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2" t="s">
@@ -6108,14 +6159,14 @@
         <v>3</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -6145,14 +6196,14 @@
         <v>6</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="K22" s="46" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -6182,13 +6233,13 @@
         <v>3</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -6319,28 +6370,28 @@
       <c r="P1"/>
       <c r="Q1"/>
       <c r="S1" s="19" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="T1" s="19" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="U1" s="20" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="V1" s="21" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" ht="17" customHeight="1" spans="1:48">
@@ -6381,22 +6432,22 @@
         <v>2</v>
       </c>
       <c r="U2" s="20" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="V2" s="21">
         <v>2</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1" spans="1:48">
@@ -6427,7 +6478,7 @@
       <c r="S3" s="19"/>
       <c r="T3" s="19"/>
       <c r="U3" s="20" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="V3" s="21">
         <v>6</v>
@@ -6472,13 +6523,13 @@
         <v>64</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="Q4"/>
       <c r="S4" s="19"/>
       <c r="T4" s="19"/>
       <c r="U4" s="20" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="V4" s="21">
         <v>1</v>
@@ -6517,21 +6568,21 @@
         <v>6</v>
       </c>
       <c r="J5" s="23" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K5" s="23" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="L5"/>
       <c r="M5" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="N5" s="2">
         <f>23*4</f>
         <v>92</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="Q5"/>
       <c r="S5" s="19">
@@ -6541,7 +6592,7 @@
         <v>10</v>
       </c>
       <c r="U5" s="20" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="V5" s="21">
         <v>1</v>
@@ -6577,23 +6628,23 @@
         <v>27</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="J6" s="25"/>
       <c r="K6" s="25"/>
       <c r="M6" s="2" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="N6" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="S6" s="19"/>
       <c r="T6" s="19"/>
       <c r="U6" s="20" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="V6" s="21">
         <v>3</v>
@@ -6619,23 +6670,23 @@
       <c r="F7" s="24"/>
       <c r="G7" s="24"/>
       <c r="I7" s="25" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="J7" s="25"/>
       <c r="K7" s="25"/>
       <c r="M7" s="2" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="N7" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="S7" s="19"/>
       <c r="T7" s="19"/>
       <c r="U7" s="20" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="V7" s="21">
         <v>1</v>
@@ -6660,7 +6711,7 @@
       <c r="J8" s="25"/>
       <c r="K8" s="25"/>
       <c r="M8" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="N8"/>
       <c r="O8"/>
@@ -6671,7 +6722,7 @@
         <v>14</v>
       </c>
       <c r="U8" s="20" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="V8" s="21">
         <v>1</v>
@@ -6708,19 +6759,19 @@
         <v>6</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="N9"/>
       <c r="S9" s="19"/>
       <c r="T9" s="19"/>
       <c r="U9" s="20" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="V9" s="21">
         <v>3</v>
@@ -6758,16 +6809,16 @@
         <v>18</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="N10"/>
       <c r="S10" s="19"/>
       <c r="T10" s="19"/>
       <c r="U10" s="20" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="V10" s="21">
         <v>1</v>
@@ -6823,7 +6874,7 @@
         <v>21</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>26</v>
@@ -6836,7 +6887,7 @@
         <v>17</v>
       </c>
       <c r="U11" s="20" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="V11" s="21">
         <v>1</v>
@@ -6889,21 +6940,21 @@
         <v>25</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>29</v>
       </c>
       <c r="N12" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="S12" s="19"/>
       <c r="T12" s="19"/>
       <c r="U12" s="20" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="V12" s="21">
         <v>3</v>
@@ -6959,7 +7010,7 @@
         <v>27</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>31</v>
@@ -6968,7 +7019,7 @@
       <c r="S13" s="19"/>
       <c r="T13" s="19"/>
       <c r="U13" s="20" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="V13" s="21">
         <v>1</v>
@@ -7021,7 +7072,7 @@
         <v>30</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>33</v>
@@ -7031,10 +7082,10 @@
         <v>5</v>
       </c>
       <c r="T14" s="19" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="U14" s="20" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="V14" s="21">
         <v>1</v>
@@ -7063,7 +7114,7 @@
     </row>
     <row r="15" ht="17" customHeight="1" spans="1:48">
       <c r="A15" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -7078,7 +7129,7 @@
         <v>32</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>35</v>
@@ -7088,7 +7139,7 @@
       <c r="S15" s="19"/>
       <c r="T15" s="19"/>
       <c r="U15" s="20" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="V15" s="21">
         <v>3</v>
@@ -7132,16 +7183,16 @@
         <v>34</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N16"/>
       <c r="S16" s="19"/>
       <c r="T16" s="19"/>
       <c r="U16" s="20" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="V16" s="21">
         <v>1</v>
@@ -7167,25 +7218,25 @@
         <v>36</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N17" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="S17" s="19">
         <v>6</v>
       </c>
       <c r="T17" s="19" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="U17" s="20" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="V17" s="21">
         <v>1</v>
@@ -7238,24 +7289,24 @@
         <v>3</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N18" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="S18" s="19"/>
       <c r="T18" s="19"/>
       <c r="U18" s="20" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="V18" s="21">
         <v>3</v>
@@ -7299,10 +7350,10 @@
         <v>6</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>47</v>
@@ -7310,7 +7361,7 @@
       <c r="S19" s="19"/>
       <c r="T19" s="19"/>
       <c r="U19" s="20" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="V19" s="21">
         <v>1</v>
@@ -7363,13 +7414,13 @@
         <v>3</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P20"/>
       <c r="S20" s="19">
@@ -7379,7 +7430,7 @@
         <v>26</v>
       </c>
       <c r="U20" s="20" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="V20" s="21">
         <v>1</v>
@@ -7407,7 +7458,7 @@
       </c>
       <c r="AF20" s="29"/>
       <c r="AG20" s="2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AH20"/>
     </row>
@@ -7437,13 +7488,13 @@
         <v>6</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N21"/>
       <c r="O21"/>
@@ -7451,7 +7502,7 @@
       <c r="S21" s="19"/>
       <c r="T21" s="19"/>
       <c r="U21" s="20" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="V21" s="21">
         <v>3</v>
@@ -7479,7 +7530,7 @@
       </c>
       <c r="AF21" s="11"/>
       <c r="AG21" s="2" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="AH21"/>
     </row>
@@ -7491,14 +7542,14 @@
         <v>3</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L22"/>
       <c r="M22" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="N22"/>
       <c r="O22"/>
@@ -7506,7 +7557,7 @@
       <c r="S22" s="19"/>
       <c r="T22" s="19"/>
       <c r="U22" s="20" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="V22" s="21">
         <v>1</v>
@@ -7531,13 +7582,13 @@
       </c>
       <c r="AF22" s="31"/>
       <c r="AG22" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="AH22"/>
     </row>
     <row r="23" ht="17" customHeight="1" spans="1:34">
       <c r="A23" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -7549,13 +7600,13 @@
         <v>3</v>
       </c>
       <c r="J23" s="32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K23" s="32" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="M23" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="N23"/>
       <c r="O23"/>
@@ -7563,16 +7614,16 @@
         <v>8</v>
       </c>
       <c r="T23" s="28" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="U23" s="20" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="V23" s="21">
         <v>1</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
@@ -7609,7 +7660,7 @@
       <c r="S24" s="19"/>
       <c r="T24" s="19"/>
       <c r="U24" s="20" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="V24" s="21">
         <v>3</v>
@@ -7665,7 +7716,7 @@
       <c r="S25" s="19"/>
       <c r="T25" s="19"/>
       <c r="U25" s="20" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="V25" s="21">
         <v>1</v>
@@ -7704,10 +7755,10 @@
         <v>9</v>
       </c>
       <c r="T26" s="28" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="U26" s="20" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="V26" s="21">
         <v>1</v>
@@ -7763,7 +7814,7 @@
       <c r="S27" s="19"/>
       <c r="T27" s="19"/>
       <c r="U27" s="20" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="V27" s="21">
         <v>3</v>
@@ -7819,7 +7870,7 @@
       <c r="S28" s="19"/>
       <c r="T28" s="19"/>
       <c r="U28" s="20" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="V28" s="21">
         <v>1</v>
@@ -7865,7 +7916,7 @@
       <c r="M29"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="P29" s="2"/>
       <c r="S29" s="19">
@@ -7875,7 +7926,7 @@
         <v>33</v>
       </c>
       <c r="U29" s="20" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="V29" s="21">
         <v>1</v>
@@ -7908,7 +7959,7 @@
       <c r="L30"/>
       <c r="M30"/>
       <c r="N30" s="1" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="O30" s="1">
         <v>6</v>
@@ -7917,7 +7968,7 @@
       <c r="S30" s="19"/>
       <c r="T30" s="19"/>
       <c r="U30" s="20" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="V30" s="21">
         <v>3</v>
@@ -7932,7 +7983,7 @@
       <c r="L31"/>
       <c r="M31"/>
       <c r="N31" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="O31" s="1">
         <v>22</v>
@@ -7941,13 +7992,13 @@
       <c r="S31" s="19"/>
       <c r="T31" s="19"/>
       <c r="U31" s="20" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="V31" s="21">
         <v>1</v>
       </c>
       <c r="X31" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
@@ -7962,7 +8013,7 @@
       <c r="L32"/>
       <c r="M32"/>
       <c r="N32" s="1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="O32" s="1">
         <v>32</v>
@@ -7975,7 +8026,7 @@
         <v>35</v>
       </c>
       <c r="U32" s="20" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="V32" s="21">
         <v>1</v>
@@ -8008,7 +8059,7 @@
       <c r="L33"/>
       <c r="M33"/>
       <c r="N33" s="1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="O33" s="1">
         <v>2</v>
@@ -8017,7 +8068,7 @@
       <c r="S33" s="19"/>
       <c r="T33" s="19"/>
       <c r="U33" s="20" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="V33" s="21">
         <v>3</v>
@@ -8048,7 +8099,7 @@
       <c r="L34"/>
       <c r="M34"/>
       <c r="N34" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="O34" s="1">
         <v>4</v>
@@ -8057,7 +8108,7 @@
       <c r="S34" s="19"/>
       <c r="T34" s="19"/>
       <c r="U34" s="20" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="V34" s="21">
         <v>1</v>
@@ -8095,16 +8146,16 @@
         <v>66</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="S35" s="19">
         <v>12</v>
       </c>
       <c r="T35" s="28" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="U35" s="20" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="V35" s="21">
         <v>1</v>
@@ -8139,7 +8190,7 @@
       <c r="S36" s="19"/>
       <c r="T36" s="19"/>
       <c r="U36" s="20" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="V36" s="21">
         <v>3</v>
@@ -8174,12 +8225,12 @@
         <v>16</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="S37" s="19"/>
       <c r="T37" s="19"/>
       <c r="U37" s="20" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="V37" s="21">
         <v>1</v>
@@ -8204,16 +8255,16 @@
         <v>1</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="S38" s="19">
         <v>13</v>
       </c>
       <c r="T38" s="28" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="U38" s="20" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="V38" s="21">
         <v>1</v>
@@ -8224,7 +8275,7 @@
       <c r="S39" s="19"/>
       <c r="T39" s="19"/>
       <c r="U39" s="20" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="V39" s="21">
         <v>3</v>
@@ -8236,7 +8287,7 @@
       <c r="S40" s="19"/>
       <c r="T40" s="19"/>
       <c r="U40" s="20" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="V40" s="21">
         <v>1</v>
@@ -8255,10 +8306,10 @@
         <v>14</v>
       </c>
       <c r="T41" s="28" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="U41" s="20" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="V41" s="21">
         <v>1</v>
@@ -8276,7 +8327,7 @@
       <c r="S42" s="19"/>
       <c r="T42" s="19"/>
       <c r="U42" s="20" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="V42" s="21">
         <v>3</v>
@@ -8294,7 +8345,7 @@
       <c r="S43" s="19"/>
       <c r="T43" s="19"/>
       <c r="U43" s="20" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="V43" s="21">
         <v>1</v>
@@ -8305,10 +8356,10 @@
         <v>15</v>
       </c>
       <c r="T44" s="28" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="U44" s="20" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="V44" s="21">
         <v>1</v>
@@ -8318,7 +8369,7 @@
       <c r="S45" s="19"/>
       <c r="T45" s="19"/>
       <c r="U45" s="20" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="V45" s="21">
         <v>3</v>
@@ -8328,7 +8379,7 @@
       <c r="S46" s="19"/>
       <c r="T46" s="19"/>
       <c r="U46" s="20" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="V46" s="21">
         <v>1</v>
@@ -8339,10 +8390,10 @@
         <v>16</v>
       </c>
       <c r="T47" s="28" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="U47" s="20" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="V47" s="21">
         <v>1</v>
@@ -8352,7 +8403,7 @@
       <c r="S48" s="19"/>
       <c r="T48" s="19"/>
       <c r="U48" s="20" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="V48" s="21">
         <v>3</v>
@@ -8362,7 +8413,7 @@
       <c r="S49" s="19"/>
       <c r="T49" s="19"/>
       <c r="U49" s="20" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="V49" s="21">
         <v>1</v>
@@ -8373,10 +8424,10 @@
         <v>17</v>
       </c>
       <c r="T50" s="28" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="U50" s="20" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="V50" s="21">
         <v>1</v>
@@ -8386,7 +8437,7 @@
       <c r="S51" s="19"/>
       <c r="T51" s="28"/>
       <c r="U51" s="20" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="V51" s="21">
         <v>3</v>
@@ -8396,7 +8447,7 @@
       <c r="S52" s="19"/>
       <c r="T52" s="19"/>
       <c r="U52" s="20" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="V52" s="21">
         <v>1</v>
@@ -8407,10 +8458,10 @@
         <v>18</v>
       </c>
       <c r="T53" s="28" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="U53" s="20" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="V53" s="21">
         <v>1</v>
@@ -8420,7 +8471,7 @@
       <c r="S54" s="19"/>
       <c r="T54" s="19"/>
       <c r="U54" s="20" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="V54" s="21">
         <v>3</v>
@@ -8430,7 +8481,7 @@
       <c r="S55" s="19"/>
       <c r="T55" s="19"/>
       <c r="U55" s="20" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="V55" s="21">
         <v>1</v>
@@ -8441,7 +8492,7 @@
         <v>19</v>
       </c>
       <c r="T56" s="19" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="U56" s="20"/>
       <c r="V56" s="21">
@@ -8453,7 +8504,7 @@
         <v>20</v>
       </c>
       <c r="T57" s="19" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="U57" s="20"/>
       <c r="V57" s="21">
@@ -8462,7 +8513,7 @@
     </row>
     <row r="58" spans="19:22">
       <c r="U58" s="16" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="V58" s="35">
         <f>SUM(V2:V57)</f>
@@ -8471,7 +8522,7 @@
     </row>
     <row r="59" ht="13.8" spans="19:22">
       <c r="U59" s="20" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="V59" s="35">
         <f>V2+V5+V8+V11+V14+V17+V20+V23+V26+V29+V32+V35+V38+V41+V44+V47+V50+V53</f>
@@ -8480,7 +8531,7 @@
     </row>
     <row r="60" ht="13.8" spans="19:22">
       <c r="U60" s="20" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="V60" s="35">
         <f>V3+V6+V9+V12+V15+V18+V21+V24+V27+V30+V33+V36+V39+V42+V45+V48+V51+V54</f>
@@ -8489,7 +8540,7 @@
     </row>
     <row r="61" ht="13.8" spans="19:22">
       <c r="U61" s="20" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="V61" s="35">
         <f>V4+V7+V10+V13+V16+V19+V22+V25+V28+V31+V34+V37+V40+V43+V46+V49+V52+V55</f>
@@ -8501,7 +8552,7 @@
     </row>
     <row r="63" spans="19:22">
       <c r="U63" s="16" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="V63" s="17">
         <f>V59+V60</f>
@@ -8510,7 +8561,7 @@
     </row>
     <row r="64" spans="19:22">
       <c r="U64" s="35" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="V64" s="35">
         <f>V63/4</f>
@@ -8602,7 +8653,7 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="I1" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
@@ -8614,10 +8665,10 @@
         <v>3</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="T1" s="4">
         <v>1</v>
@@ -8673,10 +8724,10 @@
         <v>6</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="T2" s="5">
         <v>2</v>
@@ -8689,7 +8740,7 @@
         <v>64</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:23">
@@ -8709,10 +8760,10 @@
         <v>3</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="T3" s="4">
         <v>3</v>
@@ -8725,7 +8776,7 @@
         <v>92</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" ht="19.5" customHeight="1" spans="1:23">
@@ -8775,10 +8826,10 @@
         <v>6</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="T4" s="4">
         <v>4</v>
@@ -8787,10 +8838,10 @@
         <v>17</v>
       </c>
       <c r="V4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" ht="19.5" customHeight="1" spans="1:23">
@@ -8840,22 +8891,22 @@
         <v>3</v>
       </c>
       <c r="R5" s="9" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="S5" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="T5" s="5">
         <v>5</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="V5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" ht="19.5" customHeight="1" spans="1:23">
@@ -8905,16 +8956,16 @@
         <v>6</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="T6" s="5">
         <v>6</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="V6"/>
     </row>
@@ -8962,10 +9013,10 @@
         <v>3</v>
       </c>
       <c r="R7" s="11" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="T7" s="4">
         <v>7</v>
@@ -8984,10 +9035,10 @@
         <v>6</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="S8" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="T8" s="5">
         <v>8</v>
@@ -9003,10 +9054,10 @@
         <v>3</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="T9" s="5">
         <v>9</v>
@@ -9015,10 +9066,10 @@
         <v>31</v>
       </c>
       <c r="V9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" ht="19.5" customHeight="1" spans="1:23">
@@ -9032,7 +9083,7 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="I10" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -9044,10 +9095,10 @@
         <v>3</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="T10" s="4">
         <v>10</v>
@@ -9104,10 +9155,10 @@
         <v>3</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="T11" s="4">
         <v>11</v>
@@ -9144,16 +9195,16 @@
         <v>3</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="T12" s="4">
         <v>12</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V12"/>
       <c r="W12"/>
@@ -9205,16 +9256,16 @@
         <v>3</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="T13" s="4">
         <v>13</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="V13"/>
     </row>
@@ -9265,22 +9316,22 @@
         <v>3</v>
       </c>
       <c r="R14" s="5" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="S14" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="T14" s="5">
         <v>14</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V14" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" ht="19.5" customHeight="1" spans="1:23">
@@ -9330,10 +9381,10 @@
         <v>3</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="T15" s="4">
         <v>15</v>
@@ -9342,10 +9393,10 @@
         <v>47</v>
       </c>
       <c r="V15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" ht="19.5" customHeight="1" spans="1:23">
@@ -9386,16 +9437,16 @@
         <v>3</v>
       </c>
       <c r="R16" s="5" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="S16" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="T16" s="5">
         <v>16</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" ht="19.5" customHeight="1" spans="9:21">
@@ -9409,16 +9460,16 @@
         <v>3</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="T17" s="4">
         <v>17</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" ht="19.5" customHeight="1" spans="9:21">
@@ -9426,16 +9477,16 @@
         <v>3</v>
       </c>
       <c r="R18" s="5" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="S18" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="T18" s="5">
         <v>18</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
